--- a/polls/013_professional_board_election_voting_form--polls.xlsx
+++ b/polls/013_professional_board_election_voting_form--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>election_form_page_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Poll Details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please fill out this form carefully.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eligibility Check</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Eligibility Check 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please confirm your eligibility to vote.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,20 +579,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vote</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Election Preferences</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select your preferred candidate.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vote Record</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Eligibility Check 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please confirm your eligibility to vote.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,20 +633,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vote Record</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Voting Records</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the number of votes you plan to cast.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vote Record</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Vote Options</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select all options that apply.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,10 +687,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vote Record</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Eligibility Confirmation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please confirm your eligibility to vote.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,7 +704,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +714,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eligibility Confirmation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Vote Summary</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please confirm your vote.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vote Summary</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Details</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide any additional details.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,36 +768,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eligibility Confirmation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please review your form carefully.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>election_form_page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Vote Summary</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -776,10 +793,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -838,7 +855,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>election_form_page_9_choices</t>
+          <t>election_form_page_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,7 +872,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>election_form_page_9_choices</t>
+          <t>election_form_page_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -872,7 +889,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>election_form_page_11_choices</t>
+          <t>election_form_page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,7 +906,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>election_form_page_11_choices</t>
+          <t>election_form_page_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -898,6 +915,40 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>election_form_page_8_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>election_form_page_8_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
